--- a/Data/Calculation.xlsx
+++ b/Data/Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E8DD9F-56E4-A947-84D6-EAE994FFB9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31500500-686C-EF47-A71D-D4E51E6A9D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$E$25</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$E$10</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
@@ -29,7 +29,7 @@
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$A$30</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$G$17</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
@@ -40,10 +40,10 @@
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_val" localSheetId="0" hidden="1">10</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">70</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
   </definedNames>
-  <calcPr calcId="181029" calcMode="manual"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="8">
   <si>
     <t>DeltaT_E</t>
   </si>
@@ -448,13 +448,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E2BE04-594C-6D40-82AC-766EF530A2C4}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -471,7 +471,7 @@
         <v>287.99999999999</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -491,7 +491,7 @@
         <v>287.99999999999244</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -508,7 +508,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="E5" s="1">
         <f>E3+E2+1</f>
         <v>287.99999999999</v>
@@ -517,14 +517,67 @@
         <f>122+((500-1)*(1/(1+(B3/B2))))+1</f>
         <v>500.29268292682929</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>56</v>
+      </c>
+      <c r="K5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <f>(E1)-((E1-1)*(1/(1+B3/B2)))-1</f>
         <v>69.999999999997556</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <f>J5-J7</f>
+        <v>31</v>
+      </c>
+      <c r="L6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="1">
+        <f>I8</f>
+        <v>222.76785714285711</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="1">
+        <f>500-1-M6</f>
+        <v>276.23214285714289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I8" s="1">
+        <f>(M5)-((M5-1)*(1/(1+J7/J6)))-1</f>
+        <v>222.76785714285711</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -541,7 +594,7 @@
         <v>206.00020499971299</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -553,11 +606,10 @@
         <v>6</v>
       </c>
       <c r="E10" s="1">
-        <f>E9-1-E11</f>
         <v>155.00020499971299</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -574,13 +626,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="E13" s="1">
         <f>E10+E11+1</f>
         <v>206.00020499971299</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <f>(E9)-((E9-1)*(1/(1+B11/B10)))-1</f>
         <v>50.000049999929985</v>

--- a/Data/Calculation.xlsx
+++ b/Data/Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31500500-686C-EF47-A71D-D4E51E6A9D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C854DA66-62DE-1D40-8339-F079C7D869C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
@@ -543,14 +543,14 @@
       </c>
       <c r="J6">
         <f>J5-J7</f>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
         <v>6</v>
       </c>
       <c r="M6" s="1">
         <f>I8</f>
-        <v>222.76785714285711</v>
+        <v>364.33928571428572</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -558,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
         <v>4</v>
@@ -568,13 +568,13 @@
       </c>
       <c r="M7" s="1">
         <f>500-1-M6</f>
-        <v>276.23214285714289</v>
+        <v>134.66071428571428</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="I8" s="1">
-        <f>(M5)-((M5-1)*(1/(1+J7/J6)))-1</f>
-        <v>222.76785714285711</v>
+        <f>((M5-1)*(1/(1+J7/J6)))-1</f>
+        <v>364.33928571428572</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">

--- a/Data/Calculation.xlsx
+++ b/Data/Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C854DA66-62DE-1D40-8339-F079C7D869C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84C435F-F790-6A44-9928-65DA6E562E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="8">
   <si>
     <t>DeltaT_E</t>
   </si>
@@ -521,7 +521,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
         <v>3</v>
@@ -542,15 +542,14 @@
         <v>2</v>
       </c>
       <c r="J6">
-        <f>J5-J7</f>
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="L6" t="s">
         <v>6</v>
       </c>
       <c r="M6" s="1">
         <f>I8</f>
-        <v>364.33928571428572</v>
+        <v>377.29268292682929</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -558,7 +557,8 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <f>J5-J6</f>
+        <v>31</v>
       </c>
       <c r="K7" t="s">
         <v>4</v>
@@ -567,14 +567,14 @@
         <v>7</v>
       </c>
       <c r="M7" s="1">
-        <f>500-1-M6</f>
-        <v>134.66071428571428</v>
+        <f>M5-1-M6</f>
+        <v>121.70731707317071</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="I8" s="1">
-        <f>((M5-1)*(1/(1+J7/J6)))-1</f>
-        <v>364.33928571428572</v>
+        <f>((M5-1)*(1/(1+J6/J7)))</f>
+        <v>377.29268292682929</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -624,6 +624,36 @@
       </c>
       <c r="E11" s="1">
         <v>50</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>46</v>
+      </c>
+      <c r="K11" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" s="1">
+        <f>I14</f>
+        <v>336.28260869565219</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -631,14 +661,35 @@
         <f>E10+E11+1</f>
         <v>206.00020499971299</v>
       </c>
+      <c r="I13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f>J11-J12</f>
+        <v>31</v>
+      </c>
+      <c r="K13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" t="s">
+        <v>7</v>
+      </c>
+      <c r="M13" s="1">
+        <f>M11-1-M12</f>
+        <v>162.71739130434781</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <f>(E9)-((E9-1)*(1/(1+B11/B10)))-1</f>
         <v>50.000049999929985</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I14" s="1">
+        <f>((M11-1)*(1/(1+J12/J13)))</f>
+        <v>336.28260869565219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -654,8 +705,23 @@
       <c r="E17" s="1">
         <v>82.999795000280002</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I17" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>56</v>
+      </c>
+      <c r="K17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -670,8 +736,21 @@
         <f>E17-1-E19</f>
         <v>61.999795000280002</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I18" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="L18" t="s">
+        <v>6</v>
+      </c>
+      <c r="M18" s="1">
+        <f>I20</f>
+        <v>320.78571428571428</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -687,20 +766,43 @@
       <c r="E19" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I19" t="s">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f>J17-J18</f>
+        <v>36</v>
+      </c>
+      <c r="K19" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" t="s">
+        <v>7</v>
+      </c>
+      <c r="M19" s="1">
+        <f>M17-1-M18</f>
+        <v>178.21428571428572</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I20" s="1">
+        <f>((M17-1)*(1/(1+J18/J19)))</f>
+        <v>320.78571428571428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="E21" s="1">
         <f>E18+E19+1</f>
         <v>82.999795000280002</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <f>(E17)-((E17-1)*(1/(1+B11/B10)))-1</f>
         <v>19.999950000068296</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
@@ -717,7 +819,7 @@
         <v>41.999795000000013</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>2</v>
       </c>
@@ -733,7 +835,7 @@
         <v>30.999795000000013</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>0</v>
       </c>
@@ -750,14 +852,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -767,7 +869,7 @@
         <v>41.999795000000013</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <f>(E25)-((E25-1)*(1/(1+B19/B18)))-1</f>
         <v>9.9999500000000019</v>
